--- a/frontend/public/role-info/vivoWorksheet.xlsx
+++ b/frontend/public/role-info/vivoWorksheet.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
   <workbookPr date1904="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/garybolton/Library/CloudStorage/Dropbox/Classes/NegotiationUTD/Mod 1 Table skills/Vivo Telecom/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emk120030/projects/games-platform/games/vivo/frontend/public/role-info/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EE681EF-E215-B64B-BEC4-E6E9FE4DE7F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2AFB369-4817-2E43-9FC5-EAAAB160C888}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13740" yWindow="600" windowWidth="23840" windowHeight="18060" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5560" yWindow="660" windowWidth="23840" windowHeight="17360" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -602,9 +602,7 @@
       </c>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="11">
-        <v>35</v>
-      </c>
+      <c r="E10" s="11"/>
       <c r="F10" s="4"/>
       <c r="G10" s="4"/>
       <c r="H10" s="4"/>
@@ -628,9 +626,7 @@
       </c>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
-      <c r="E12" s="11">
-        <v>0</v>
-      </c>
+      <c r="E12" s="11"/>
       <c r="F12" s="4"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
@@ -654,9 +650,7 @@
       </c>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
-      <c r="E14" s="11">
-        <v>6</v>
-      </c>
+      <c r="E14" s="11"/>
       <c r="F14" s="4"/>
       <c r="G14" s="4"/>
       <c r="H14" s="4"/>
@@ -692,9 +686,9 @@
       </c>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
-      <c r="E17" s="13">
+      <c r="E17" s="13" t="str">
         <f>IF(AND(E10="",E12="",E14=""),"",SUM(E10,E12,E14))</f>
-        <v>41</v>
+        <v/>
       </c>
       <c r="F17" s="4"/>
       <c r="G17" s="4"/>
@@ -741,9 +735,7 @@
       </c>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="11">
-        <v>40</v>
-      </c>
+      <c r="E21" s="11"/>
       <c r="F21" s="4"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
@@ -767,9 +759,7 @@
       </c>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
-      <c r="E23" s="11">
-        <v>0</v>
-      </c>
+      <c r="E23" s="11"/>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
       <c r="H23" s="4"/>
@@ -805,9 +795,9 @@
       </c>
       <c r="C26" s="4"/>
       <c r="D26" s="4"/>
-      <c r="E26" s="16">
+      <c r="E26" s="16" t="str">
         <f>IF(AND(E21="",E23=""),"",SUM(E21,E23))</f>
-        <v>40</v>
+        <v/>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -856,9 +846,9 @@
         <v>23</v>
       </c>
       <c r="D30" s="4"/>
-      <c r="E30" s="16">
+      <c r="E30" s="16" t="str">
         <f>IF(OR(E17="",E26=""),"",E17-E26)</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
